--- a/SSIS-Project/Timesheets/Teolan/Teolan_Govender_June_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Teolan/Teolan_Govender_June_FinalWeek.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northerndata-my.sharepoint.com/personal/teolan_govender_sambeconsulting_com/Documents/Documents/Timesheets and Leave/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Teolan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2114" documentId="13_ncr:1_{18456319-F974-4A60-AFC5-4E049C41B553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9A0B388-FAE1-443C-B266-F1AF40ADABBE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DFFAF4-33F9-4023-862B-9C5E27026D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr" sheetId="10" r:id="rId1"/>
@@ -2079,13 +2079,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2101,21 +2116,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -18883,27 +18883,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="135" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="141" t="s">
+      <c r="B9" s="132" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="141" t="s">
+      <c r="C9" s="133"/>
+      <c r="D9" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="142"/>
+      <c r="E9" s="133"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -18912,103 +18912,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="134" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132" t="s">
+      <c r="C10" s="134"/>
+      <c r="D10" s="134" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="132"/>
+      <c r="E10" s="134"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="139" t="s">
+      <c r="G10" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="136" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="132" t="s">
+      <c r="C11" s="137"/>
+      <c r="D11" s="134" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="132"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="136" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="130"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
+      <c r="B13" s="136"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="130"/>
-      <c r="C16" s="131"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="138" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="134"/>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="135"/>
+      <c r="B17" s="139"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -19024,16 +19024,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -19043,6 +19033,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -19147,10 +19147,10 @@
         <v>81</v>
       </c>
       <c r="B11" s="117">
-        <v>46094</v>
+        <v>46155</v>
       </c>
       <c r="C11" s="117">
-        <v>46095</v>
+        <v>46156</v>
       </c>
       <c r="D11" s="87">
         <v>1</v>
